--- a/v2/design/RGX-2-002-BOM.xlsx
+++ b/v2/design/RGX-2-002-BOM.xlsx
@@ -42,7 +42,7 @@
     <t>ReGenX v2 — Bill of Materials   ·   RGX-2-002 Rev A</t>
   </si>
   <si>
-    <t>Against RGX-2-001 Rev C / RGX-2-100 Rev D  ·  2026-08-02.  Prices approximate CAD, August 2026, before tax/shipping — blue cells are editable estimates; update them after quoting. Sourcing assumes delivery to Ontario.</t>
+    <t>Against RGX-2-001 Rev D / RGX-2-100 Rev E  ·  2026-09-29.  Prices approximate CAD, August 2026, before tax/shipping — blue cells are editable estimates; update them after quoting. Sourcing assumes delivery to Ontario.</t>
   </si>
   <si>
     <t>Summary (CAD)</t>
@@ -447,7 +447,7 @@
     <t>Ceramic caps</t>
   </si>
   <si>
-    <t>2x 100 nF &gt;=16 V X7R; 1 nF &gt;=50 V C0G</t>
+    <t>2x 100 nF &gt;=16 V X7R; 10 nF &gt;=50 V C0G</t>
   </si>
   <si>
     <t>Ceramic assortment kit - Amazon.ca</t>
@@ -552,10 +552,10 @@
     <t>Single 9-pin Higo Z910, NOT the separate 6-way J1 drawn on Sheet 3</t>
   </si>
   <si>
-    <t>W1 redefined as Z910 splitter - electrically identical. Queued as drawing Rev E. Pinouts vary: continuity-map before power</t>
-  </si>
-  <si>
-    <t>Drawing Rev E</t>
+    <t>W1 redefined as Z910 splitter - electrically identical. Queued as drawing Rev F. Pinouts vary: continuity-map before power</t>
+  </si>
+  <si>
+    <t>Drawing Rev F</t>
   </si>
   <si>
     <t>Back-EMF, coasting</t>

--- a/v2/design/RGX-2-002-BOM.xlsx
+++ b/v2/design/RGX-2-002-BOM.xlsx
@@ -42,7 +42,7 @@
     <t>ReGenX v2 — Bill of Materials   ·   RGX-2-002 Rev A</t>
   </si>
   <si>
-    <t>Against RGX-2-001 Rev D / RGX-2-100 Rev E  ·  2026-09-29.  Prices approximate CAD, August 2026, before tax/shipping — blue cells are editable estimates; update them after quoting. Sourcing assumes delivery to Ontario.</t>
+    <t>Against RGX-2-001 Rev E / RGX-2-100 Rev F  ·  2026-09-29.  Prices approximate CAD, August 2026, before tax/shipping — blue cells are editable estimates; update them after quoting. Sourcing assumes delivery to Ontario.</t>
   </si>
   <si>
     <t>Summary (CAD)</t>
@@ -549,13 +549,13 @@
     <t>Cable / W1</t>
   </si>
   <si>
-    <t>Single 9-pin Higo Z910, NOT the separate 6-way J1 drawn on Sheet 3</t>
-  </si>
-  <si>
-    <t>W1 redefined as Z910 splitter - electrically identical. Queued as drawing Rev F. Pinouts vary: continuity-map before power</t>
-  </si>
-  <si>
-    <t>Drawing Rev F</t>
+    <t>Single 9-pin Higo Z910, drawn as J1 from drawing Rev F</t>
+  </si>
+  <si>
+    <t>W1 is the Z910 splitter - electrically identical. Drawn at Rev F. Pinouts vary: continuity-map before power</t>
+  </si>
+  <si>
+    <t>Done at drawing Rev F</t>
   </si>
   <si>
     <t>Back-EMF, coasting</t>
